--- a/artfynd/A 19101-2020 artfynd.xlsx
+++ b/artfynd/A 19101-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123173467</v>
       </c>
       <c r="B2" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19101-2020 artfynd.xlsx
+++ b/artfynd/A 19101-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123173467</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19101-2020 artfynd.xlsx
+++ b/artfynd/A 19101-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123173467</v>
       </c>
       <c r="B2" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19101-2020 artfynd.xlsx
+++ b/artfynd/A 19101-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123173467</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
